--- a/data/UBF_course_data.xlsx
+++ b/data/UBF_course_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/scheduling/Campus-Scheduling/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_2269D1ACD3305E53AB393211595ED87656CDDB19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCC4A271-8BA0-4893-92A9-4366E3B204BC}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_023931AAD310DB6FFF1B3E11595ED87656CDEC01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A060B360-0335-453D-ACAB-C646AFBA0E7D}"/>
   <bookViews>
     <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="205">
   <si>
     <t>DepartmentName</t>
   </si>
@@ -187,6 +187,12 @@
     <t>Türk Vergi Sistemi</t>
   </si>
   <si>
+    <t>TDP301</t>
+  </si>
+  <si>
+    <t>Toplumsal Duyarlılık ve Katkı</t>
+  </si>
+  <si>
     <t>Pazarlama</t>
   </si>
   <si>
@@ -310,6 +316,15 @@
     <t>Lojistik ve Tedarik Zinciri Yönetimi</t>
   </si>
   <si>
+    <t>TDP 300</t>
+  </si>
+  <si>
+    <t>Toplumsal Destek Projeleri</t>
+  </si>
+  <si>
+    <t>TDP 301</t>
+  </si>
+  <si>
     <t>Sigortacılık</t>
   </si>
   <si>
@@ -506,6 +521,12 @@
   </si>
   <si>
     <t>Yönetim Bilişim Sistemleri</t>
+  </si>
+  <si>
+    <t>PFE 304</t>
+  </si>
+  <si>
+    <t>Özel Öğretim Yöntemleri</t>
   </si>
   <si>
     <t>YBS 152</t>
@@ -737,33 +758,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E4D04688-5675-42FD-A99C-FF258B4037BE}" name="Table1" displayName="Table1" ref="A1:J101" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:J101" xr:uid="{E4D04688-5675-42FD-A99C-FF258B4037BE}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Finans ve Bankacılık"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="2"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J101">
-    <sortCondition ref="J1:J101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{010BEB2A-2788-40DD-8A95-9F4221BF390A}" name="Table1" displayName="Table1" ref="A1:J105" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:J105" xr:uid="{010BEB2A-2788-40DD-8A95-9F4221BF390A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J105">
+    <sortCondition ref="J1:J105"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{B07CBDCC-CF4F-4FFE-96F0-7F97B6F3AAAD}" name="DepartmentName"/>
-    <tableColumn id="2" xr3:uid="{CF8F3D36-CD79-4188-9A2F-6706EC7AADF1}" name="CourseCode"/>
-    <tableColumn id="3" xr3:uid="{3D4CA313-0E27-4DE3-BEEA-B3509B2AEF89}" name="CourseName"/>
-    <tableColumn id="4" xr3:uid="{79D9EA9C-34F4-44A6-A5C5-4CBD16725969}" name="AKTS"/>
-    <tableColumn id="5" xr3:uid="{94CA8355-2D62-414E-B49E-DFE029EC1EE0}" name="KREDI"/>
-    <tableColumn id="6" xr3:uid="{0CC8597E-66D9-4E5A-AFB1-3371E7C9687D}" name="Lab"/>
-    <tableColumn id="7" xr3:uid="{F10100A8-7A9D-4B20-9C3A-BF8C151A0B99}" name="SINIF"/>
-    <tableColumn id="8" xr3:uid="{DF760AF1-F26B-49AA-9911-F51B4864E5DD}" name="ZOR_SEC"/>
-    <tableColumn id="9" xr3:uid="{252E26C2-8EAE-4269-BD78-564BBA8B82BF}" name="InstructorUserId"/>
-    <tableColumn id="10" xr3:uid="{D3866C7C-E9DA-41C1-AC8A-CD900018E05B}" name="OgrenciSayisi"/>
+    <tableColumn id="1" xr3:uid="{AEF05F01-5251-4C7F-BC94-44769B783F37}" name="DepartmentName"/>
+    <tableColumn id="2" xr3:uid="{612775CE-4B9E-48BD-AAAB-2AAA4DE6B8BC}" name="CourseCode"/>
+    <tableColumn id="3" xr3:uid="{FCACDFDC-4586-4DF1-A972-84398E9294AB}" name="CourseName"/>
+    <tableColumn id="4" xr3:uid="{97AD7ED0-8B40-4886-B675-3B65D452842B}" name="AKTS"/>
+    <tableColumn id="5" xr3:uid="{5AE6A1FB-7F86-4AF8-9485-54EF76734AF5}" name="KREDI"/>
+    <tableColumn id="6" xr3:uid="{8DE0D720-F427-4DFB-A7DA-675FC7A70604}" name="Lab"/>
+    <tableColumn id="7" xr3:uid="{C992AD60-7230-46D7-8190-C7BF32A36B20}" name="SINIF"/>
+    <tableColumn id="8" xr3:uid="{40F2A096-85F0-4B29-8DC5-2B93BF434F4A}" name="ZOR_SEC"/>
+    <tableColumn id="9" xr3:uid="{F6BB14AE-2DF7-4DF4-8013-8E0D8EE2673A}" name="InstructorUserId"/>
+    <tableColumn id="10" xr3:uid="{2E243B00-87DD-444F-8604-05BC5B7CD0AB}" name="OgrenciSayisi"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1054,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="17.73046875" customWidth="1"/>
@@ -1097,15 +1107,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -1129,21 +1139,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1152,59 +1162,59 @@
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I3">
         <v>2767522</v>
       </c>
       <c r="J3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4">
+        <v>2767522</v>
+      </c>
+      <c r="J4">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4">
-        <v>2550042</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>67</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -1219,24 +1229,24 @@
         <v>13</v>
       </c>
       <c r="I5">
-        <v>2767522</v>
+        <v>2550042</v>
       </c>
       <c r="J5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1251,88 +1261,88 @@
         <v>13</v>
       </c>
       <c r="I6">
-        <v>2550322</v>
+        <v>2767522</v>
       </c>
       <c r="J6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>183</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="D7">
         <v>5</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" t="s">
         <v>13</v>
       </c>
       <c r="I7">
+        <v>2550322</v>
+      </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8">
         <v>1650231</v>
       </c>
-      <c r="J7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="J8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
         <v>101</v>
       </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8">
-        <v>2460217</v>
-      </c>
-      <c r="J8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>55</v>
-      </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -1347,21 +1357,21 @@
         <v>13</v>
       </c>
       <c r="I9">
-        <v>2767522</v>
+        <v>2460217</v>
       </c>
       <c r="J9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>168</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -1373,33 +1383,33 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I10">
-        <v>2750113</v>
+        <v>2560131</v>
       </c>
       <c r="J10">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1411,21 +1421,21 @@
         <v>13</v>
       </c>
       <c r="I11">
-        <v>2570142</v>
+        <v>2767522</v>
       </c>
       <c r="J11">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -1437,27 +1447,27 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="I12">
-        <v>2460217</v>
+        <v>2750113</v>
       </c>
       <c r="J12">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1472,24 +1482,24 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="I13">
-        <v>5570334</v>
+        <v>2570142</v>
       </c>
       <c r="J13">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -1501,7 +1511,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="s">
         <v>32</v>
@@ -1510,24 +1520,24 @@
         <v>2460217</v>
       </c>
       <c r="J14">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1536,13 +1546,13 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I15">
-        <v>2767522</v>
+        <v>5570334</v>
       </c>
       <c r="J15">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
@@ -1550,10 +1560,10 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -1565,30 +1575,30 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="s">
         <v>32</v>
       </c>
       <c r="I16">
-        <v>2680031</v>
+        <v>2460217</v>
       </c>
       <c r="J16">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1606,18 +1616,18 @@
         <v>2767522</v>
       </c>
       <c r="J17">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -1629,30 +1639,30 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="s">
         <v>32</v>
       </c>
       <c r="I18">
-        <v>2440530</v>
+        <v>2680031</v>
       </c>
       <c r="J18">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1667,85 +1677,85 @@
         <v>13</v>
       </c>
       <c r="I19">
+        <v>2767522</v>
+      </c>
+      <c r="J19">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20">
+        <v>2440530</v>
+      </c>
+      <c r="J20">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21">
         <v>2550322</v>
       </c>
-      <c r="J19">
+      <c r="J21">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" t="s">
-        <v>121</v>
-      </c>
-      <c r="C20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D20">
-        <v>5</v>
-      </c>
-      <c r="E20">
-        <v>3</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>3</v>
-      </c>
-      <c r="H20" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20">
-        <v>5575334</v>
-      </c>
-      <c r="J20">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>96</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
         <v>127</v>
-      </c>
-      <c r="C21" t="s">
-        <v>128</v>
-      </c>
-      <c r="D21">
-        <v>5</v>
-      </c>
-      <c r="E21">
-        <v>4</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>3</v>
-      </c>
-      <c r="H21" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21">
-        <v>2460310</v>
-      </c>
-      <c r="J21">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" t="s">
-        <v>118</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -1763,27 +1773,27 @@
         <v>13</v>
       </c>
       <c r="I22">
-        <v>2550042</v>
+        <v>5575334</v>
       </c>
       <c r="J22">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>56</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1792,59 +1802,59 @@
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="I23">
-        <v>2570142</v>
+        <v>7450141</v>
       </c>
       <c r="J23">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" t="s">
         <v>32</v>
       </c>
       <c r="I24">
-        <v>5780238</v>
+        <v>2460310</v>
       </c>
       <c r="J24">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -1862,53 +1872,53 @@
         <v>2550042</v>
       </c>
       <c r="J25">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" t="s">
         <v>55</v>
       </c>
-      <c r="B26" t="s">
-        <v>58</v>
-      </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D26">
         <v>2</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26" t="s">
         <v>13</v>
       </c>
       <c r="I26">
-        <v>2767522</v>
+        <v>2460217</v>
       </c>
       <c r="J26">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -1923,24 +1933,24 @@
         <v>32</v>
       </c>
       <c r="I27">
-        <v>2750113</v>
+        <v>2570142</v>
       </c>
       <c r="J27">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -1949,80 +1959,80 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I28">
-        <v>3655367</v>
+        <v>5780238</v>
       </c>
       <c r="J28">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>3</v>
+      </c>
+      <c r="H29" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29">
+        <v>2550042</v>
+      </c>
+      <c r="J29">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30">
+        <v>2767522</v>
+      </c>
+      <c r="J30">
         <v>44</v>
-      </c>
-      <c r="D29">
-        <v>4</v>
-      </c>
-      <c r="E29">
-        <v>3</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>3</v>
-      </c>
-      <c r="H29" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29">
-        <v>2440530</v>
-      </c>
-      <c r="J29">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>10</v>
-      </c>
-      <c r="B30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30">
-        <v>4</v>
-      </c>
-      <c r="E30">
-        <v>3</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>3</v>
-      </c>
-      <c r="H30" t="s">
-        <v>13</v>
-      </c>
-      <c r="I30">
-        <v>2550042</v>
-      </c>
-      <c r="J30">
-        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
@@ -2030,10 +2040,10 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -2045,27 +2055,27 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" t="s">
         <v>32</v>
       </c>
       <c r="I31">
-        <v>2540145</v>
+        <v>2750113</v>
       </c>
       <c r="J31">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -2086,21 +2096,21 @@
         <v>3655367</v>
       </c>
       <c r="J32">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -2118,21 +2128,21 @@
         <v>2440530</v>
       </c>
       <c r="J33">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>161</v>
+        <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>194</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>195</v>
+        <v>46</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -2144,56 +2154,56 @@
         <v>3</v>
       </c>
       <c r="H34" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34">
+        <v>2550042</v>
+      </c>
+      <c r="J34">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35" t="s">
         <v>32</v>
       </c>
-      <c r="I34">
-        <v>2565028</v>
-      </c>
-      <c r="J34">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" t="s">
-        <v>107</v>
-      </c>
-      <c r="C35" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35">
-        <v>5</v>
-      </c>
-      <c r="E35">
-        <v>3</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>2</v>
-      </c>
-      <c r="H35" t="s">
-        <v>13</v>
-      </c>
       <c r="I35">
-        <v>2550042</v>
+        <v>2540145</v>
       </c>
       <c r="J35">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -2205,27 +2215,27 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
       </c>
       <c r="I36">
-        <v>4565554</v>
+        <v>3655367</v>
       </c>
       <c r="J36">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -2237,59 +2247,59 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
       </c>
       <c r="I37">
-        <v>2570142</v>
+        <v>2440530</v>
       </c>
       <c r="J37">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" t="s">
+        <v>201</v>
+      </c>
+      <c r="C38" t="s">
+        <v>202</v>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38">
+        <v>3</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>3</v>
+      </c>
+      <c r="H38" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38">
+        <v>2565028</v>
+      </c>
+      <c r="J38">
         <v>55</v>
-      </c>
-      <c r="B38" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38">
-        <v>3</v>
-      </c>
-      <c r="E38">
-        <v>3</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>3</v>
-      </c>
-      <c r="H38" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38">
-        <v>2510318</v>
-      </c>
-      <c r="J38">
-        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -2307,21 +2317,21 @@
         <v>13</v>
       </c>
       <c r="I39">
-        <v>2540145</v>
+        <v>2550042</v>
       </c>
       <c r="J39">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C40" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="D40">
         <v>5</v>
@@ -2339,21 +2349,21 @@
         <v>13</v>
       </c>
       <c r="I40">
-        <v>2550322</v>
+        <v>4565554</v>
       </c>
       <c r="J40">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C41" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -2368,27 +2378,27 @@
         <v>2</v>
       </c>
       <c r="H41" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="I41">
         <v>2570142</v>
       </c>
       <c r="J41">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -2397,27 +2407,27 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" t="s">
         <v>13</v>
       </c>
       <c r="I42">
-        <v>2400356</v>
+        <v>2510318</v>
       </c>
       <c r="J42">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D43">
         <v>5</v>
@@ -2429,27 +2439,27 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43" t="s">
         <v>13</v>
       </c>
       <c r="I43">
-        <v>2400356</v>
+        <v>2540145</v>
       </c>
       <c r="J43">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C44" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="D44">
         <v>5</v>
@@ -2467,56 +2477,56 @@
         <v>13</v>
       </c>
       <c r="I44">
-        <v>3655367</v>
+        <v>2550322</v>
       </c>
       <c r="J44">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" t="s">
+        <v>69</v>
+      </c>
+      <c r="D45">
+        <v>5</v>
+      </c>
+      <c r="E45">
+        <v>3</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>2</v>
+      </c>
+      <c r="H45" t="s">
+        <v>32</v>
+      </c>
+      <c r="I45">
+        <v>2570142</v>
+      </c>
+      <c r="J45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
         <v>10</v>
       </c>
-      <c r="B45" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45">
-        <v>4</v>
-      </c>
-      <c r="E45">
-        <v>3</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>2</v>
-      </c>
-      <c r="H45" t="s">
-        <v>13</v>
-      </c>
-      <c r="I45">
-        <v>2680031</v>
-      </c>
-      <c r="J45">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>55</v>
-      </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="C46" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -2525,27 +2535,27 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46" t="s">
         <v>13</v>
       </c>
       <c r="I46">
-        <v>2480350</v>
+        <v>2400356</v>
       </c>
       <c r="J46">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="D47">
         <v>5</v>
@@ -2563,181 +2573,181 @@
         <v>13</v>
       </c>
       <c r="I47">
+        <v>2400356</v>
+      </c>
+      <c r="J47">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>101</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" t="s">
+        <v>116</v>
+      </c>
+      <c r="D48">
+        <v>5</v>
+      </c>
+      <c r="E48">
+        <v>3</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>2</v>
+      </c>
+      <c r="H48" t="s">
+        <v>13</v>
+      </c>
+      <c r="I48">
+        <v>3655367</v>
+      </c>
+      <c r="J48">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49">
+        <v>4</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49" t="s">
+        <v>13</v>
+      </c>
+      <c r="I49">
+        <v>2680031</v>
+      </c>
+      <c r="J49">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50">
+        <v>3</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>3</v>
+      </c>
+      <c r="H50" t="s">
+        <v>13</v>
+      </c>
+      <c r="I50">
+        <v>2480350</v>
+      </c>
+      <c r="J50">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51">
+        <v>5</v>
+      </c>
+      <c r="E51">
+        <v>3</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>3</v>
+      </c>
+      <c r="H51" t="s">
+        <v>13</v>
+      </c>
+      <c r="I51">
         <v>7450141</v>
       </c>
-      <c r="J47">
+      <c r="J51">
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" t="s">
-        <v>80</v>
-      </c>
-      <c r="C48" t="s">
-        <v>81</v>
-      </c>
-      <c r="D48">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" t="s">
+        <v>82</v>
+      </c>
+      <c r="C52" t="s">
+        <v>83</v>
+      </c>
+      <c r="D52">
         <v>6</v>
       </c>
-      <c r="E48">
-        <v>3</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>3</v>
-      </c>
-      <c r="H48" t="s">
-        <v>13</v>
-      </c>
-      <c r="I48">
+      <c r="E52">
+        <v>3</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>3</v>
+      </c>
+      <c r="H52" t="s">
+        <v>13</v>
+      </c>
+      <c r="I52">
         <v>3844334</v>
       </c>
-      <c r="J48">
+      <c r="J52">
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" t="s">
-        <v>73</v>
-      </c>
-      <c r="D49">
-        <v>6</v>
-      </c>
-      <c r="E49">
-        <v>3</v>
-      </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <v>2</v>
-      </c>
-      <c r="H49" t="s">
-        <v>13</v>
-      </c>
-      <c r="I49">
-        <v>3844334</v>
-      </c>
-      <c r="J49">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" t="s">
-        <v>84</v>
-      </c>
-      <c r="C50" t="s">
-        <v>85</v>
-      </c>
-      <c r="D50">
-        <v>4</v>
-      </c>
-      <c r="E50">
-        <v>3</v>
-      </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
-      <c r="G50">
-        <v>3</v>
-      </c>
-      <c r="H50" t="s">
-        <v>13</v>
-      </c>
-      <c r="I50">
-        <v>4465113</v>
-      </c>
-      <c r="J50">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>55</v>
-      </c>
-      <c r="B51" t="s">
-        <v>92</v>
-      </c>
-      <c r="C51" t="s">
-        <v>93</v>
-      </c>
-      <c r="D51">
-        <v>3</v>
-      </c>
-      <c r="E51">
-        <v>2</v>
-      </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-      <c r="G51">
-        <v>3</v>
-      </c>
-      <c r="H51" t="s">
-        <v>32</v>
-      </c>
-      <c r="I51">
-        <v>2767522</v>
-      </c>
-      <c r="J51">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" t="s">
-        <v>71</v>
-      </c>
-      <c r="D52">
-        <v>5</v>
-      </c>
-      <c r="E52">
-        <v>3</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>2</v>
-      </c>
-      <c r="H52" t="s">
-        <v>13</v>
-      </c>
-      <c r="I52">
-        <v>2566164</v>
-      </c>
-      <c r="J52">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>55</v>
-      </c>
-      <c r="B53" t="s">
-        <v>68</v>
-      </c>
-      <c r="C53" t="s">
-        <v>69</v>
       </c>
       <c r="D53">
         <v>6</v>
@@ -2755,207 +2765,207 @@
         <v>13</v>
       </c>
       <c r="I53">
+        <v>3844334</v>
+      </c>
+      <c r="J53">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" t="s">
+        <v>87</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>3</v>
+      </c>
+      <c r="H54" t="s">
+        <v>13</v>
+      </c>
+      <c r="I54">
+        <v>4465113</v>
+      </c>
+      <c r="J54">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" t="s">
+        <v>94</v>
+      </c>
+      <c r="C55" t="s">
+        <v>95</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>3</v>
+      </c>
+      <c r="H55" t="s">
+        <v>32</v>
+      </c>
+      <c r="I55">
+        <v>2767522</v>
+      </c>
+      <c r="J55">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" t="s">
+        <v>73</v>
+      </c>
+      <c r="D56">
+        <v>5</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+      <c r="H56" t="s">
+        <v>13</v>
+      </c>
+      <c r="I56">
+        <v>2566164</v>
+      </c>
+      <c r="J56">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" t="s">
+        <v>70</v>
+      </c>
+      <c r="C57" t="s">
+        <v>71</v>
+      </c>
+      <c r="D57">
+        <v>6</v>
+      </c>
+      <c r="E57">
+        <v>3</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>2</v>
+      </c>
+      <c r="H57" t="s">
+        <v>13</v>
+      </c>
+      <c r="I57">
         <v>2480350</v>
       </c>
-      <c r="J53">
+      <c r="J57">
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54" t="s">
-        <v>77</v>
-      </c>
-      <c r="C54" t="s">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" t="s">
         <v>15</v>
       </c>
-      <c r="D54">
-        <v>3</v>
-      </c>
-      <c r="E54">
-        <v>3</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>2</v>
-      </c>
-      <c r="H54" t="s">
-        <v>13</v>
-      </c>
-      <c r="I54">
+      <c r="D58">
+        <v>3</v>
+      </c>
+      <c r="E58">
+        <v>3</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>2</v>
+      </c>
+      <c r="H58" t="s">
+        <v>13</v>
+      </c>
+      <c r="I58">
         <v>2680031</v>
       </c>
-      <c r="J54">
+      <c r="J58">
         <v>87</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>161</v>
-      </c>
-      <c r="B55" t="s">
-        <v>163</v>
-      </c>
-      <c r="C55" t="s">
-        <v>57</v>
-      </c>
-      <c r="D55">
-        <v>4</v>
-      </c>
-      <c r="E55">
-        <v>2</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
-      <c r="H55" t="s">
-        <v>13</v>
-      </c>
-      <c r="I55">
-        <v>2560131</v>
-      </c>
-      <c r="J55">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>161</v>
-      </c>
-      <c r="B56" t="s">
-        <v>164</v>
-      </c>
-      <c r="C56" t="s">
-        <v>165</v>
-      </c>
-      <c r="D56">
-        <v>4</v>
-      </c>
-      <c r="E56">
-        <v>3</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>1</v>
-      </c>
-      <c r="H56" t="s">
-        <v>13</v>
-      </c>
-      <c r="I56">
-        <v>2560131</v>
-      </c>
-      <c r="J56">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>161</v>
-      </c>
-      <c r="B57" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" t="s">
-        <v>67</v>
-      </c>
-      <c r="D57">
-        <v>5</v>
-      </c>
-      <c r="E57">
-        <v>3</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <v>1</v>
-      </c>
-      <c r="H57" t="s">
-        <v>13</v>
-      </c>
-      <c r="I57">
-        <v>2450302</v>
-      </c>
-      <c r="J57">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>129</v>
-      </c>
-      <c r="B58" t="s">
-        <v>140</v>
-      </c>
-      <c r="C58" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58">
-        <v>5</v>
-      </c>
-      <c r="E58">
-        <v>3</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <v>2</v>
-      </c>
-      <c r="H58" t="s">
-        <v>13</v>
-      </c>
-      <c r="I58">
-        <v>2510318</v>
-      </c>
-      <c r="J58">
-        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>166</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D59">
         <v>4</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" t="s">
         <v>13</v>
       </c>
       <c r="I59">
-        <v>2556335</v>
+        <v>2560131</v>
       </c>
       <c r="J59">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B60" t="s">
         <v>171</v>
@@ -2973,27 +2983,27 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H60" t="s">
         <v>13</v>
       </c>
       <c r="I60">
-        <v>2650432</v>
+        <v>2560131</v>
       </c>
       <c r="J60">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>166</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>169</v>
       </c>
       <c r="C61" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="D61">
         <v>5</v>
@@ -3011,469 +3021,469 @@
         <v>13</v>
       </c>
       <c r="I61">
+        <v>2450302</v>
+      </c>
+      <c r="J61">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62">
+        <v>5</v>
+      </c>
+      <c r="E62">
+        <v>3</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>2</v>
+      </c>
+      <c r="H62" t="s">
+        <v>13</v>
+      </c>
+      <c r="I62">
+        <v>2510318</v>
+      </c>
+      <c r="J62">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63">
+        <v>4</v>
+      </c>
+      <c r="E63">
+        <v>3</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>2</v>
+      </c>
+      <c r="H63" t="s">
+        <v>13</v>
+      </c>
+      <c r="I63">
+        <v>2556335</v>
+      </c>
+      <c r="J63">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>166</v>
+      </c>
+      <c r="B64" t="s">
+        <v>178</v>
+      </c>
+      <c r="C64" t="s">
+        <v>179</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64">
+        <v>3</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>2</v>
+      </c>
+      <c r="H64" t="s">
+        <v>13</v>
+      </c>
+      <c r="I64">
+        <v>2650432</v>
+      </c>
+      <c r="J64">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>10</v>
+      </c>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65">
+        <v>5</v>
+      </c>
+      <c r="E65">
+        <v>3</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
+        <v>13</v>
+      </c>
+      <c r="I65">
         <v>3750338</v>
       </c>
-      <c r="J61">
+      <c r="J65">
         <v>96</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A62" t="s">
-        <v>55</v>
-      </c>
-      <c r="B62" t="s">
-        <v>74</v>
-      </c>
-      <c r="C62" t="s">
-        <v>75</v>
-      </c>
-      <c r="D62">
-        <v>4</v>
-      </c>
-      <c r="E62">
-        <v>3</v>
-      </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
-      <c r="G62">
-        <v>2</v>
-      </c>
-      <c r="H62" t="s">
-        <v>13</v>
-      </c>
-      <c r="I62">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>57</v>
+      </c>
+      <c r="B66" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66" t="s">
+        <v>77</v>
+      </c>
+      <c r="D66">
+        <v>4</v>
+      </c>
+      <c r="E66">
+        <v>3</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>2</v>
+      </c>
+      <c r="H66" t="s">
+        <v>13</v>
+      </c>
+      <c r="I66">
         <v>4465113</v>
       </c>
-      <c r="J62">
+      <c r="J66">
         <v>98</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A63" t="s">
-        <v>161</v>
-      </c>
-      <c r="B63" t="s">
-        <v>182</v>
-      </c>
-      <c r="C63" t="s">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>166</v>
+      </c>
+      <c r="B67" t="s">
+        <v>189</v>
+      </c>
+      <c r="C67" t="s">
+        <v>103</v>
+      </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67">
+        <v>3</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="H67" t="s">
+        <v>13</v>
+      </c>
+      <c r="I67">
+        <v>2540145</v>
+      </c>
+      <c r="J67">
         <v>98</v>
       </c>
-      <c r="D63">
-        <v>3</v>
-      </c>
-      <c r="E63">
-        <v>3</v>
-      </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
-      <c r="G63">
-        <v>2</v>
-      </c>
-      <c r="H63" t="s">
-        <v>13</v>
-      </c>
-      <c r="I63">
-        <v>2540145</v>
-      </c>
-      <c r="J63">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A64" t="s">
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
         <v>10</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B68" t="s">
         <v>18</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C68" t="s">
         <v>19</v>
       </c>
-      <c r="D64">
-        <v>4</v>
-      </c>
-      <c r="E64">
-        <v>3</v>
-      </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
-      <c r="G64">
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68">
+        <v>3</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
         <v>1</v>
       </c>
-      <c r="H64" t="s">
-        <v>13</v>
-      </c>
-      <c r="I64">
+      <c r="H68" t="s">
+        <v>13</v>
+      </c>
+      <c r="I68">
         <v>4565554</v>
       </c>
-      <c r="J64">
+      <c r="J68">
         <v>99</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" t="s">
-        <v>86</v>
-      </c>
-      <c r="C65" t="s">
-        <v>87</v>
-      </c>
-      <c r="D65">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>57</v>
+      </c>
+      <c r="B69" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" t="s">
+        <v>89</v>
+      </c>
+      <c r="D69">
         <v>6</v>
       </c>
-      <c r="E65">
-        <v>3</v>
-      </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
-      <c r="G65">
-        <v>3</v>
-      </c>
-      <c r="H65" t="s">
-        <v>13</v>
-      </c>
-      <c r="I65">
+      <c r="E69">
+        <v>3</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>3</v>
+      </c>
+      <c r="H69" t="s">
+        <v>13</v>
+      </c>
+      <c r="I69">
         <v>2480350</v>
       </c>
-      <c r="J65">
+      <c r="J69">
         <v>99</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A66" t="s">
-        <v>129</v>
-      </c>
-      <c r="B66" t="s">
-        <v>130</v>
-      </c>
-      <c r="C66" t="s">
-        <v>65</v>
-      </c>
-      <c r="D66">
-        <v>5</v>
-      </c>
-      <c r="E66">
-        <v>3</v>
-      </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
-      <c r="G66">
-        <v>1</v>
-      </c>
-      <c r="H66" t="s">
-        <v>13</v>
-      </c>
-      <c r="I66">
-        <v>3750338</v>
-      </c>
-      <c r="J66">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A67" t="s">
-        <v>129</v>
-      </c>
-      <c r="B67" t="s">
-        <v>141</v>
-      </c>
-      <c r="C67" t="s">
-        <v>142</v>
-      </c>
-      <c r="D67">
-        <v>4</v>
-      </c>
-      <c r="E67">
-        <v>3</v>
-      </c>
-      <c r="F67">
-        <v>0</v>
-      </c>
-      <c r="G67">
-        <v>2</v>
-      </c>
-      <c r="H67" t="s">
-        <v>13</v>
-      </c>
-      <c r="I67">
-        <v>4550431</v>
-      </c>
-      <c r="J67">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A68" t="s">
-        <v>161</v>
-      </c>
-      <c r="B68" t="s">
-        <v>169</v>
-      </c>
-      <c r="C68" t="s">
-        <v>170</v>
-      </c>
-      <c r="D68">
-        <v>4</v>
-      </c>
-      <c r="E68">
-        <v>3</v>
-      </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-      <c r="G68">
-        <v>2</v>
-      </c>
-      <c r="H68" t="s">
-        <v>13</v>
-      </c>
-      <c r="I68">
-        <v>2650432</v>
-      </c>
-      <c r="J68">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A69" t="s">
-        <v>161</v>
-      </c>
-      <c r="B69" t="s">
-        <v>175</v>
-      </c>
-      <c r="C69" t="s">
-        <v>176</v>
-      </c>
-      <c r="D69">
-        <v>4</v>
-      </c>
-      <c r="E69">
-        <v>3</v>
-      </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
-      <c r="G69">
-        <v>2</v>
-      </c>
-      <c r="H69" t="s">
-        <v>13</v>
-      </c>
-      <c r="I69">
-        <v>1650231</v>
-      </c>
-      <c r="J69">
-        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
+        <v>134</v>
+      </c>
+      <c r="B70" t="s">
+        <v>135</v>
+      </c>
+      <c r="C70" t="s">
+        <v>67</v>
+      </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+      <c r="E70">
+        <v>3</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70" t="s">
+        <v>13</v>
+      </c>
+      <c r="I70">
+        <v>3750338</v>
+      </c>
+      <c r="J70">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>134</v>
+      </c>
+      <c r="B71" t="s">
+        <v>146</v>
+      </c>
+      <c r="C71" t="s">
+        <v>147</v>
+      </c>
+      <c r="D71">
+        <v>4</v>
+      </c>
+      <c r="E71">
+        <v>3</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>2</v>
+      </c>
+      <c r="H71" t="s">
+        <v>13</v>
+      </c>
+      <c r="I71">
+        <v>4550431</v>
+      </c>
+      <c r="J71">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>166</v>
+      </c>
+      <c r="B72" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D72">
+        <v>4</v>
+      </c>
+      <c r="E72">
+        <v>3</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>2</v>
+      </c>
+      <c r="H72" t="s">
+        <v>13</v>
+      </c>
+      <c r="I72">
+        <v>2650432</v>
+      </c>
+      <c r="J72">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>166</v>
+      </c>
+      <c r="B73" t="s">
+        <v>182</v>
+      </c>
+      <c r="C73" t="s">
+        <v>183</v>
+      </c>
+      <c r="D73">
+        <v>4</v>
+      </c>
+      <c r="E73">
+        <v>3</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+      <c r="H73" t="s">
+        <v>13</v>
+      </c>
+      <c r="I73">
+        <v>1650231</v>
+      </c>
+      <c r="J73">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
         <v>10</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B74" t="s">
         <v>26</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C74" t="s">
         <v>27</v>
       </c>
-      <c r="D70">
-        <v>4</v>
-      </c>
-      <c r="E70">
-        <v>3</v>
-      </c>
-      <c r="F70">
+      <c r="D74">
+        <v>4</v>
+      </c>
+      <c r="E74">
+        <v>3</v>
+      </c>
+      <c r="F74">
         <v>1</v>
       </c>
-      <c r="G70">
-        <v>2</v>
-      </c>
-      <c r="H70" t="s">
-        <v>13</v>
-      </c>
-      <c r="I70">
+      <c r="G74">
+        <v>2</v>
+      </c>
+      <c r="H74" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74">
         <v>2556335</v>
       </c>
-      <c r="J70">
+      <c r="J74">
         <v>105</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A71" t="s">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
         <v>10</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B75" t="s">
         <v>14</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C75" t="s">
         <v>15</v>
       </c>
-      <c r="D71">
+      <c r="D75">
         <v>5</v>
       </c>
-      <c r="E71">
-        <v>3</v>
-      </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
-      <c r="G71">
+      <c r="E75">
+        <v>3</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
         <v>1</v>
       </c>
-      <c r="H71" t="s">
-        <v>13</v>
-      </c>
-      <c r="I71">
+      <c r="H75" t="s">
+        <v>13</v>
+      </c>
+      <c r="I75">
         <v>2750113</v>
       </c>
-      <c r="J71">
+      <c r="J75">
         <v>107</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A72" t="s">
-        <v>129</v>
-      </c>
-      <c r="B72" t="s">
-        <v>132</v>
-      </c>
-      <c r="C72" t="s">
-        <v>133</v>
-      </c>
-      <c r="D72">
-        <v>4</v>
-      </c>
-      <c r="E72">
-        <v>3</v>
-      </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
-      <c r="G72">
-        <v>1</v>
-      </c>
-      <c r="H72" t="s">
-        <v>13</v>
-      </c>
-      <c r="I72">
-        <v>6546123</v>
-      </c>
-      <c r="J72">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A73" t="s">
-        <v>129</v>
-      </c>
-      <c r="B73" t="s">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>134</v>
+      </c>
+      <c r="B76" t="s">
         <v>137</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C76" t="s">
         <v>138</v>
-      </c>
-      <c r="D73">
-        <v>3</v>
-      </c>
-      <c r="E73">
-        <v>3</v>
-      </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
-      <c r="G73">
-        <v>2</v>
-      </c>
-      <c r="H73" t="s">
-        <v>13</v>
-      </c>
-      <c r="I73">
-        <v>6546123</v>
-      </c>
-      <c r="J73">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A74" t="s">
-        <v>129</v>
-      </c>
-      <c r="B74" t="s">
-        <v>139</v>
-      </c>
-      <c r="C74" t="s">
-        <v>98</v>
-      </c>
-      <c r="D74">
-        <v>5</v>
-      </c>
-      <c r="E74">
-        <v>3</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-      <c r="G74">
-        <v>2</v>
-      </c>
-      <c r="H74" t="s">
-        <v>13</v>
-      </c>
-      <c r="I74">
-        <v>2750113</v>
-      </c>
-      <c r="J74">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A75" t="s">
-        <v>129</v>
-      </c>
-      <c r="B75" t="s">
-        <v>143</v>
-      </c>
-      <c r="C75" t="s">
-        <v>144</v>
-      </c>
-      <c r="D75">
-        <v>4</v>
-      </c>
-      <c r="E75">
-        <v>3</v>
-      </c>
-      <c r="F75">
-        <v>0</v>
-      </c>
-      <c r="G75">
-        <v>2</v>
-      </c>
-      <c r="H75" t="s">
-        <v>32</v>
-      </c>
-      <c r="I75">
-        <v>4670514</v>
-      </c>
-      <c r="J75">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A76" t="s">
-        <v>10</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="s">
-        <v>17</v>
       </c>
       <c r="D76">
         <v>4</v>
@@ -3491,57 +3501,57 @@
         <v>13</v>
       </c>
       <c r="I76">
-        <v>2400356</v>
+        <v>6546123</v>
       </c>
       <c r="J76">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B77" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="D77">
+        <v>3</v>
+      </c>
+      <c r="E77">
+        <v>3</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>2</v>
+      </c>
+      <c r="H77" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77">
+        <v>6546123</v>
+      </c>
+      <c r="J77">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>134</v>
+      </c>
+      <c r="B78" t="s">
+        <v>144</v>
+      </c>
+      <c r="C78" t="s">
+        <v>103</v>
+      </c>
+      <c r="D78">
         <v>5</v>
       </c>
-      <c r="E77">
-        <v>3</v>
-      </c>
-      <c r="F77">
-        <v>0</v>
-      </c>
-      <c r="G77">
-        <v>2</v>
-      </c>
-      <c r="H77" t="s">
-        <v>13</v>
-      </c>
-      <c r="I77">
-        <v>2564167</v>
-      </c>
-      <c r="J77">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A78" t="s">
-        <v>161</v>
-      </c>
-      <c r="B78" t="s">
-        <v>168</v>
-      </c>
-      <c r="C78" t="s">
-        <v>65</v>
-      </c>
-      <c r="D78">
-        <v>4</v>
-      </c>
       <c r="E78">
         <v>3</v>
       </c>
@@ -3549,30 +3559,30 @@
         <v>0</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="s">
         <v>13</v>
       </c>
       <c r="I78">
-        <v>2564167</v>
+        <v>2750113</v>
       </c>
       <c r="J78">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="B79" t="s">
-        <v>196</v>
+        <v>148</v>
       </c>
       <c r="C79" t="s">
-        <v>197</v>
+        <v>149</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E79">
         <v>3</v>
@@ -3581,30 +3591,30 @@
         <v>0</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79" t="s">
         <v>32</v>
       </c>
       <c r="I79">
-        <v>3668244</v>
+        <v>4670514</v>
       </c>
       <c r="J79">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>161</v>
+        <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c r="C80" t="s">
-        <v>167</v>
+        <v>17</v>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E80">
         <v>3</v>
@@ -3619,24 +3629,24 @@
         <v>13</v>
       </c>
       <c r="I80">
-        <v>2565028</v>
+        <v>2400356</v>
       </c>
       <c r="J80">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="B81" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="C81" t="s">
-        <v>174</v>
+        <v>25</v>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E81">
         <v>3</v>
@@ -3651,24 +3661,24 @@
         <v>13</v>
       </c>
       <c r="I81">
-        <v>2565028</v>
+        <v>2564167</v>
       </c>
       <c r="J81">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B82" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C82" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E82">
         <v>3</v>
@@ -3677,27 +3687,27 @@
         <v>0</v>
       </c>
       <c r="G82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H82" t="s">
         <v>13</v>
       </c>
       <c r="I82">
-        <v>2400356</v>
+        <v>2564167</v>
       </c>
       <c r="J82">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="B83" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="C83" t="s">
-        <v>67</v>
+        <v>204</v>
       </c>
       <c r="D83">
         <v>5</v>
@@ -3709,53 +3719,53 @@
         <v>0</v>
       </c>
       <c r="G83">
+        <v>3</v>
+      </c>
+      <c r="H83" t="s">
+        <v>32</v>
+      </c>
+      <c r="I83">
+        <v>3668244</v>
+      </c>
+      <c r="J83">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>166</v>
+      </c>
+      <c r="B84" t="s">
+        <v>173</v>
+      </c>
+      <c r="C84" t="s">
+        <v>174</v>
+      </c>
+      <c r="D84">
+        <v>5</v>
+      </c>
+      <c r="E84">
+        <v>3</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
         <v>1</v>
       </c>
-      <c r="H83" t="s">
-        <v>13</v>
-      </c>
-      <c r="I83">
-        <v>1780136</v>
-      </c>
-      <c r="J83">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A84" t="s">
-        <v>55</v>
-      </c>
-      <c r="B84" t="s">
-        <v>76</v>
-      </c>
-      <c r="C84" t="s">
-        <v>27</v>
-      </c>
-      <c r="D84">
-        <v>4</v>
-      </c>
-      <c r="E84">
-        <v>3</v>
-      </c>
-      <c r="F84">
-        <v>0</v>
-      </c>
-      <c r="G84">
-        <v>2</v>
-      </c>
       <c r="H84" t="s">
         <v>13</v>
       </c>
       <c r="I84">
-        <v>2566164</v>
+        <v>2565028</v>
       </c>
       <c r="J84">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B85" t="s">
         <v>180</v>
@@ -3779,152 +3789,152 @@
         <v>13</v>
       </c>
       <c r="I85">
+        <v>2565028</v>
+      </c>
+      <c r="J85">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>166</v>
+      </c>
+      <c r="B86" t="s">
+        <v>186</v>
+      </c>
+      <c r="C86" t="s">
+        <v>27</v>
+      </c>
+      <c r="D86">
+        <v>3</v>
+      </c>
+      <c r="E86">
+        <v>3</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>2</v>
+      </c>
+      <c r="H86" t="s">
+        <v>13</v>
+      </c>
+      <c r="I86">
+        <v>2400356</v>
+      </c>
+      <c r="J86">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>134</v>
+      </c>
+      <c r="B87" t="s">
+        <v>136</v>
+      </c>
+      <c r="C87" t="s">
+        <v>69</v>
+      </c>
+      <c r="D87">
+        <v>5</v>
+      </c>
+      <c r="E87">
+        <v>3</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87" t="s">
+        <v>13</v>
+      </c>
+      <c r="I87">
+        <v>1780136</v>
+      </c>
+      <c r="J87">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>57</v>
+      </c>
+      <c r="B88" t="s">
+        <v>78</v>
+      </c>
+      <c r="C88" t="s">
+        <v>27</v>
+      </c>
+      <c r="D88">
+        <v>4</v>
+      </c>
+      <c r="E88">
+        <v>3</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>2</v>
+      </c>
+      <c r="H88" t="s">
+        <v>13</v>
+      </c>
+      <c r="I88">
+        <v>2566164</v>
+      </c>
+      <c r="J88">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>166</v>
+      </c>
+      <c r="B89" t="s">
+        <v>187</v>
+      </c>
+      <c r="C89" t="s">
+        <v>188</v>
+      </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89">
+        <v>3</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>2</v>
+      </c>
+      <c r="H89" t="s">
+        <v>13</v>
+      </c>
+      <c r="I89">
         <v>2450302</v>
       </c>
-      <c r="J85">
+      <c r="J89">
         <v>132</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A86" t="s">
-        <v>161</v>
-      </c>
-      <c r="B86" t="s">
-        <v>192</v>
-      </c>
-      <c r="C86" t="s">
-        <v>193</v>
-      </c>
-      <c r="D86">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>166</v>
+      </c>
+      <c r="B90" t="s">
+        <v>199</v>
+      </c>
+      <c r="C90" t="s">
+        <v>200</v>
+      </c>
+      <c r="D90">
         <v>5</v>
-      </c>
-      <c r="E86">
-        <v>3</v>
-      </c>
-      <c r="F86">
-        <v>0</v>
-      </c>
-      <c r="G86">
-        <v>3</v>
-      </c>
-      <c r="H86" t="s">
-        <v>32</v>
-      </c>
-      <c r="I86">
-        <v>5564242</v>
-      </c>
-      <c r="J86">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A87" t="s">
-        <v>129</v>
-      </c>
-      <c r="B87" t="s">
-        <v>147</v>
-      </c>
-      <c r="C87" t="s">
-        <v>148</v>
-      </c>
-      <c r="D87">
-        <v>3</v>
-      </c>
-      <c r="E87">
-        <v>3</v>
-      </c>
-      <c r="F87">
-        <v>0</v>
-      </c>
-      <c r="G87">
-        <v>3</v>
-      </c>
-      <c r="H87" t="s">
-        <v>13</v>
-      </c>
-      <c r="I87">
-        <v>1652363</v>
-      </c>
-      <c r="J87">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A88" t="s">
-        <v>129</v>
-      </c>
-      <c r="B88" t="s">
-        <v>134</v>
-      </c>
-      <c r="C88" t="s">
-        <v>135</v>
-      </c>
-      <c r="D88">
-        <v>4</v>
-      </c>
-      <c r="E88">
-        <v>3</v>
-      </c>
-      <c r="F88">
-        <v>0</v>
-      </c>
-      <c r="G88">
-        <v>1</v>
-      </c>
-      <c r="H88" t="s">
-        <v>13</v>
-      </c>
-      <c r="I88">
-        <v>1700063</v>
-      </c>
-      <c r="J88">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A89" t="s">
-        <v>161</v>
-      </c>
-      <c r="B89" t="s">
-        <v>177</v>
-      </c>
-      <c r="C89" t="s">
-        <v>178</v>
-      </c>
-      <c r="D89">
-        <v>4</v>
-      </c>
-      <c r="E89">
-        <v>3</v>
-      </c>
-      <c r="F89">
-        <v>0</v>
-      </c>
-      <c r="G89">
-        <v>2</v>
-      </c>
-      <c r="H89" t="s">
-        <v>13</v>
-      </c>
-      <c r="I89">
-        <v>1450512</v>
-      </c>
-      <c r="J89">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A90" t="s">
-        <v>129</v>
-      </c>
-      <c r="B90" t="s">
-        <v>149</v>
-      </c>
-      <c r="C90" t="s">
-        <v>91</v>
-      </c>
-      <c r="D90">
-        <v>4</v>
       </c>
       <c r="E90">
         <v>3</v>
@@ -3939,21 +3949,21 @@
         <v>32</v>
       </c>
       <c r="I90">
-        <v>4550431</v>
+        <v>5564242</v>
       </c>
       <c r="J90">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B91" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C91" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="D91">
         <v>3</v>
@@ -3974,326 +3984,454 @@
         <v>1652363</v>
       </c>
       <c r="J91">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>134</v>
+      </c>
+      <c r="B92" t="s">
+        <v>139</v>
+      </c>
+      <c r="C92" t="s">
+        <v>140</v>
+      </c>
+      <c r="D92">
+        <v>4</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92" t="s">
+        <v>13</v>
+      </c>
+      <c r="I92">
+        <v>1700063</v>
+      </c>
+      <c r="J92">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>166</v>
+      </c>
+      <c r="B93" t="s">
+        <v>184</v>
+      </c>
+      <c r="C93" t="s">
+        <v>185</v>
+      </c>
+      <c r="D93">
+        <v>4</v>
+      </c>
+      <c r="E93">
+        <v>3</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>2</v>
+      </c>
+      <c r="H93" t="s">
+        <v>13</v>
+      </c>
+      <c r="I93">
+        <v>1450512</v>
+      </c>
+      <c r="J93">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>134</v>
+      </c>
+      <c r="B94" t="s">
+        <v>154</v>
+      </c>
+      <c r="C94" t="s">
+        <v>93</v>
+      </c>
+      <c r="D94">
+        <v>4</v>
+      </c>
+      <c r="E94">
+        <v>3</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>3</v>
+      </c>
+      <c r="H94" t="s">
+        <v>32</v>
+      </c>
+      <c r="I94">
+        <v>4550431</v>
+      </c>
+      <c r="J94">
         <v>142</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A92" t="s">
-        <v>129</v>
-      </c>
-      <c r="B92" t="s">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>134</v>
+      </c>
+      <c r="B95" t="s">
+        <v>155</v>
+      </c>
+      <c r="C95" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95">
+        <v>3</v>
+      </c>
+      <c r="E95">
+        <v>3</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>3</v>
+      </c>
+      <c r="H95" t="s">
+        <v>13</v>
+      </c>
+      <c r="I95">
+        <v>1652363</v>
+      </c>
+      <c r="J95">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>134</v>
+      </c>
+      <c r="B96" t="s">
+        <v>156</v>
+      </c>
+      <c r="C96" t="s">
+        <v>157</v>
+      </c>
+      <c r="D96">
+        <v>4</v>
+      </c>
+      <c r="E96">
+        <v>3</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>3</v>
+      </c>
+      <c r="H96" t="s">
+        <v>13</v>
+      </c>
+      <c r="I96">
+        <v>4670514</v>
+      </c>
+      <c r="J96">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>134</v>
+      </c>
+      <c r="B97" t="s">
+        <v>160</v>
+      </c>
+      <c r="C97" t="s">
+        <v>161</v>
+      </c>
+      <c r="D97">
+        <v>4</v>
+      </c>
+      <c r="E97">
+        <v>3</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>3</v>
+      </c>
+      <c r="H97" t="s">
+        <v>13</v>
+      </c>
+      <c r="I97">
+        <v>4550431</v>
+      </c>
+      <c r="J97">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>134</v>
+      </c>
+      <c r="B98" t="s">
+        <v>164</v>
+      </c>
+      <c r="C98" t="s">
+        <v>165</v>
+      </c>
+      <c r="D98">
+        <v>4</v>
+      </c>
+      <c r="E98">
+        <v>3</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>3</v>
+      </c>
+      <c r="H98" t="s">
+        <v>13</v>
+      </c>
+      <c r="I98">
+        <v>4670514</v>
+      </c>
+      <c r="J98">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>166</v>
+      </c>
+      <c r="B99" t="s">
+        <v>192</v>
+      </c>
+      <c r="C99" t="s">
+        <v>193</v>
+      </c>
+      <c r="D99">
+        <v>5</v>
+      </c>
+      <c r="E99">
+        <v>3</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>3</v>
+      </c>
+      <c r="H99" t="s">
+        <v>13</v>
+      </c>
+      <c r="I99">
+        <v>1650231</v>
+      </c>
+      <c r="J99">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>166</v>
+      </c>
+      <c r="B100" t="s">
+        <v>194</v>
+      </c>
+      <c r="C100" t="s">
+        <v>38</v>
+      </c>
+      <c r="D100">
+        <v>5</v>
+      </c>
+      <c r="E100">
+        <v>3</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>3</v>
+      </c>
+      <c r="H100" t="s">
+        <v>13</v>
+      </c>
+      <c r="I100">
+        <v>2450302</v>
+      </c>
+      <c r="J100">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>134</v>
+      </c>
+      <c r="B101" t="s">
+        <v>162</v>
+      </c>
+      <c r="C101" t="s">
+        <v>163</v>
+      </c>
+      <c r="D101">
+        <v>4</v>
+      </c>
+      <c r="E101">
+        <v>3</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>3</v>
+      </c>
+      <c r="H101" t="s">
+        <v>32</v>
+      </c>
+      <c r="I101">
+        <v>6590408</v>
+      </c>
+      <c r="J101">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>166</v>
+      </c>
+      <c r="B102" t="s">
+        <v>197</v>
+      </c>
+      <c r="C102" t="s">
+        <v>198</v>
+      </c>
+      <c r="D102">
+        <v>5</v>
+      </c>
+      <c r="E102">
+        <v>3</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>3</v>
+      </c>
+      <c r="H102" t="s">
+        <v>13</v>
+      </c>
+      <c r="I102">
+        <v>2550322</v>
+      </c>
+      <c r="J102">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>134</v>
+      </c>
+      <c r="B103" t="s">
+        <v>158</v>
+      </c>
+      <c r="C103" t="s">
+        <v>159</v>
+      </c>
+      <c r="D103">
+        <v>4</v>
+      </c>
+      <c r="E103">
+        <v>3</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>3</v>
+      </c>
+      <c r="H103" t="s">
+        <v>13</v>
+      </c>
+      <c r="I103">
+        <v>1700063</v>
+      </c>
+      <c r="J103">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>134</v>
+      </c>
+      <c r="B104" t="s">
+        <v>150</v>
+      </c>
+      <c r="C104" t="s">
         <v>151</v>
       </c>
-      <c r="C92" t="s">
-        <v>152</v>
-      </c>
-      <c r="D92">
-        <v>4</v>
-      </c>
-      <c r="E92">
-        <v>3</v>
-      </c>
-      <c r="F92">
-        <v>0</v>
-      </c>
-      <c r="G92">
-        <v>3</v>
-      </c>
-      <c r="H92" t="s">
-        <v>13</v>
-      </c>
-      <c r="I92">
-        <v>4670514</v>
-      </c>
-      <c r="J92">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A93" t="s">
-        <v>129</v>
-      </c>
-      <c r="B93" t="s">
-        <v>155</v>
-      </c>
-      <c r="C93" t="s">
-        <v>156</v>
-      </c>
-      <c r="D93">
-        <v>4</v>
-      </c>
-      <c r="E93">
-        <v>3</v>
-      </c>
-      <c r="F93">
-        <v>0</v>
-      </c>
-      <c r="G93">
-        <v>3</v>
-      </c>
-      <c r="H93" t="s">
-        <v>13</v>
-      </c>
-      <c r="I93">
-        <v>4550431</v>
-      </c>
-      <c r="J93">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A94" t="s">
-        <v>129</v>
-      </c>
-      <c r="B94" t="s">
-        <v>159</v>
-      </c>
-      <c r="C94" t="s">
-        <v>160</v>
-      </c>
-      <c r="D94">
-        <v>4</v>
-      </c>
-      <c r="E94">
-        <v>3</v>
-      </c>
-      <c r="F94">
-        <v>0</v>
-      </c>
-      <c r="G94">
-        <v>3</v>
-      </c>
-      <c r="H94" t="s">
-        <v>13</v>
-      </c>
-      <c r="I94">
-        <v>4670514</v>
-      </c>
-      <c r="J94">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A95" t="s">
-        <v>161</v>
-      </c>
-      <c r="B95" t="s">
-        <v>185</v>
-      </c>
-      <c r="C95" t="s">
-        <v>186</v>
-      </c>
-      <c r="D95">
+      <c r="D104">
+        <v>4</v>
+      </c>
+      <c r="E104">
+        <v>3</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>2</v>
+      </c>
+      <c r="H104" t="s">
+        <v>32</v>
+      </c>
+      <c r="I104">
+        <v>1652363</v>
+      </c>
+      <c r="J104">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>166</v>
+      </c>
+      <c r="B105" t="s">
+        <v>195</v>
+      </c>
+      <c r="C105" t="s">
+        <v>196</v>
+      </c>
+      <c r="D105">
         <v>5</v>
       </c>
-      <c r="E95">
-        <v>3</v>
-      </c>
-      <c r="F95">
-        <v>0</v>
-      </c>
-      <c r="G95">
-        <v>3</v>
-      </c>
-      <c r="H95" t="s">
-        <v>13</v>
-      </c>
-      <c r="I95">
-        <v>1650231</v>
-      </c>
-      <c r="J95">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A96" t="s">
-        <v>161</v>
-      </c>
-      <c r="B96" t="s">
-        <v>187</v>
-      </c>
-      <c r="C96" t="s">
-        <v>38</v>
-      </c>
-      <c r="D96">
-        <v>5</v>
-      </c>
-      <c r="E96">
-        <v>3</v>
-      </c>
-      <c r="F96">
-        <v>0</v>
-      </c>
-      <c r="G96">
-        <v>3</v>
-      </c>
-      <c r="H96" t="s">
-        <v>13</v>
-      </c>
-      <c r="I96">
-        <v>2450302</v>
-      </c>
-      <c r="J96">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A97" t="s">
-        <v>129</v>
-      </c>
-      <c r="B97" t="s">
-        <v>157</v>
-      </c>
-      <c r="C97" t="s">
-        <v>158</v>
-      </c>
-      <c r="D97">
-        <v>4</v>
-      </c>
-      <c r="E97">
-        <v>3</v>
-      </c>
-      <c r="F97">
-        <v>0</v>
-      </c>
-      <c r="G97">
-        <v>3</v>
-      </c>
-      <c r="H97" t="s">
-        <v>32</v>
-      </c>
-      <c r="I97">
-        <v>6590408</v>
-      </c>
-      <c r="J97">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A98" t="s">
-        <v>161</v>
-      </c>
-      <c r="B98" t="s">
-        <v>190</v>
-      </c>
-      <c r="C98" t="s">
-        <v>191</v>
-      </c>
-      <c r="D98">
-        <v>5</v>
-      </c>
-      <c r="E98">
-        <v>3</v>
-      </c>
-      <c r="F98">
-        <v>0</v>
-      </c>
-      <c r="G98">
-        <v>3</v>
-      </c>
-      <c r="H98" t="s">
-        <v>13</v>
-      </c>
-      <c r="I98">
-        <v>2550322</v>
-      </c>
-      <c r="J98">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A99" t="s">
-        <v>129</v>
-      </c>
-      <c r="B99" t="s">
-        <v>153</v>
-      </c>
-      <c r="C99" t="s">
-        <v>154</v>
-      </c>
-      <c r="D99">
-        <v>4</v>
-      </c>
-      <c r="E99">
-        <v>3</v>
-      </c>
-      <c r="F99">
-        <v>0</v>
-      </c>
-      <c r="G99">
-        <v>3</v>
-      </c>
-      <c r="H99" t="s">
-        <v>13</v>
-      </c>
-      <c r="I99">
-        <v>1700063</v>
-      </c>
-      <c r="J99">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A100" t="s">
-        <v>129</v>
-      </c>
-      <c r="B100" t="s">
-        <v>145</v>
-      </c>
-      <c r="C100" t="s">
-        <v>146</v>
-      </c>
-      <c r="D100">
-        <v>4</v>
-      </c>
-      <c r="E100">
-        <v>3</v>
-      </c>
-      <c r="F100">
-        <v>0</v>
-      </c>
-      <c r="G100">
-        <v>2</v>
-      </c>
-      <c r="H100" t="s">
-        <v>32</v>
-      </c>
-      <c r="I100">
-        <v>1652363</v>
-      </c>
-      <c r="J100">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A101" t="s">
-        <v>161</v>
-      </c>
-      <c r="B101" t="s">
-        <v>188</v>
-      </c>
-      <c r="C101" t="s">
-        <v>189</v>
-      </c>
-      <c r="D101">
-        <v>5</v>
-      </c>
-      <c r="E101">
-        <v>3</v>
-      </c>
-      <c r="F101">
-        <v>0</v>
-      </c>
-      <c r="G101">
-        <v>3</v>
-      </c>
-      <c r="H101" t="s">
-        <v>13</v>
-      </c>
-      <c r="I101">
+      <c r="E105">
+        <v>3</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>3</v>
+      </c>
+      <c r="H105" t="s">
+        <v>13</v>
+      </c>
+      <c r="I105">
         <v>1450512</v>
       </c>
-      <c r="J101">
+      <c r="J105">
         <v>190</v>
       </c>
     </row>
